--- a/diseases/d183/2005-2009.xlsx
+++ b/diseases/d183/2005-2009.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3818,6 +3923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4108,6 +4223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4253,6 +4373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4398,6 +4523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4543,6 +4673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4688,6 +4823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4833,6 +4973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4978,6 +5123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5123,6 +5273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5268,6 +5423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5413,6 +5573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5558,6 +5723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5703,6 +5873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5848,6 +6023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5993,6 +6173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6138,6 +6323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6283,6 +6473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6428,6 +6623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6573,6 +6773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6718,6 +6923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6863,6 +7073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7008,6 +7223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7153,6 +7373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7298,6 +7523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7443,6 +7673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7588,6 +7823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7733,6 +7973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7878,6 +8123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8023,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8168,6 +8423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8313,6 +8573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8458,6 +8723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8603,6 +8873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8748,6 +9023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8893,6 +9173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9038,6 +9323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9183,6 +9473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9326,6 +9621,11 @@
       <c r="S61" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">

--- a/diseases/d183/2005-2009.xlsx
+++ b/diseases/d183/2005-2009.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1218,11 +1173,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,22 +1185,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1368,11 +1308,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,22 +1320,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1518,11 +1443,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,22 +1455,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1668,11 +1578,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,22 +1590,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1818,11 +1713,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,22 +1725,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1968,11 +1848,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1985,22 +1860,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2118,11 +1983,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,22 +1995,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2268,11 +2118,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2285,22 +2130,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2418,11 +2253,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2435,22 +2265,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2568,11 +2388,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2585,22 +2400,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2718,11 +2523,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2735,22 +2535,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2868,11 +2658,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2885,22 +2670,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3018,11 +2793,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,22 +2805,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3168,11 +2928,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3185,22 +2940,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3318,11 +3063,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3075,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3468,11 +3198,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3485,22 +3210,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3618,11 +3333,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3635,22 +3345,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3768,11 +3468,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,22 +3480,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3918,11 +3603,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3935,22 +3615,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4068,11 +3738,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4085,22 +3750,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4218,11 +3873,6 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4235,22 +3885,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4368,11 +4008,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4385,22 +4020,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4518,11 +4143,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4535,22 +4155,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4668,11 +4278,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4685,22 +4290,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4818,11 +4413,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4835,22 +4425,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4968,11 +4548,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4985,22 +4560,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5118,11 +4683,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5135,22 +4695,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5268,11 +4818,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5285,22 +4830,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5418,11 +4953,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5435,22 +4965,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5568,11 +5088,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5585,22 +5100,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5718,11 +5223,6 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5735,22 +5235,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5868,11 +5358,6 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5885,22 +5370,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6018,11 +5493,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6035,22 +5505,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6168,11 +5628,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6185,22 +5640,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6318,11 +5763,6 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6335,22 +5775,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6468,11 +5898,6 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6485,22 +5910,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6618,11 +6033,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6635,22 +6045,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6768,11 +6168,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6785,22 +6180,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6918,11 +6303,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6935,22 +6315,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7068,11 +6438,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7085,22 +6450,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7218,11 +6573,6 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7235,22 +6585,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7368,11 +6708,6 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7385,22 +6720,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7518,11 +6843,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7535,22 +6855,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7668,11 +6978,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7685,22 +6990,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7818,11 +7113,6 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7835,22 +7125,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7968,11 +7248,6 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7985,22 +7260,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8118,11 +7383,6 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8135,22 +7395,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8268,11 +7518,6 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8285,22 +7530,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8418,11 +7653,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8435,22 +7665,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8568,11 +7788,6 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8585,22 +7800,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8718,11 +7923,6 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8735,22 +7935,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8868,11 +8058,6 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8885,22 +8070,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9018,11 +8193,6 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9035,22 +8205,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9168,11 +8328,6 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9185,22 +8340,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9318,11 +8463,6 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9335,22 +8475,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9468,11 +8598,6 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9485,22 +8610,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9618,11 +8733,6 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9635,22 +8745,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>

--- a/diseases/d183/2005-2009.xlsx
+++ b/diseases/d183/2005-2009.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,12 +785,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,12 +935,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,12 +1085,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1173,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,12 +1235,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1308,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,12 +1385,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1443,6 +1518,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,12 +1535,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1578,6 +1668,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,12 +1685,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1713,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,12 +1835,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1848,6 +1968,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1860,12 +1985,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -1983,6 +2118,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1995,12 +2135,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2118,6 +2268,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2130,12 +2285,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2253,6 +2418,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2265,12 +2435,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2388,6 +2568,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2400,12 +2585,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2523,6 +2718,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,12 +2735,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2658,6 +2868,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,12 +2885,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2793,6 +3018,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2805,12 +3035,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2928,6 +3168,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2940,12 +3185,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3063,6 +3318,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3075,12 +3335,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3198,6 +3468,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3210,12 +3485,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3333,6 +3618,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3345,12 +3635,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3468,6 +3768,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3480,12 +3785,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3603,6 +3918,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3615,12 +3935,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3738,6 +4068,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3750,12 +4085,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3873,6 +4218,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3885,12 +4235,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4008,6 +4368,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4020,12 +4385,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4143,6 +4518,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4155,12 +4535,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4278,6 +4668,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4290,12 +4685,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4413,6 +4818,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4425,12 +4835,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4548,6 +4968,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4560,12 +4985,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4683,6 +5118,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4695,12 +5135,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4818,6 +5268,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4830,12 +5285,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -4953,6 +5418,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4965,12 +5435,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5088,6 +5568,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5100,12 +5585,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5223,6 +5718,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5235,12 +5735,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5358,6 +5868,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5370,12 +5885,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5493,6 +6018,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5505,12 +6035,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5628,6 +6168,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5640,12 +6185,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5763,6 +6318,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5775,12 +6335,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -5898,6 +6468,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5910,12 +6485,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6033,6 +6618,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6045,12 +6635,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6168,6 +6768,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6180,12 +6785,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6303,6 +6918,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6315,12 +6935,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6438,6 +7068,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6450,12 +7085,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6573,6 +7218,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6585,12 +7235,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6708,6 +7368,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6720,12 +7385,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -6843,6 +7518,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6855,12 +7535,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -6978,6 +7668,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6990,12 +7685,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7113,6 +7818,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7125,12 +7835,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7248,6 +7968,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7260,12 +7985,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7383,6 +8118,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7395,12 +8135,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7518,6 +8268,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7530,12 +8285,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -7653,6 +8418,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7665,12 +8435,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -7788,6 +8568,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7800,12 +8585,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -7923,6 +8718,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7935,12 +8735,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8058,6 +8868,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8070,12 +8885,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8193,6 +9018,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8205,12 +9035,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8328,6 +9168,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8340,12 +9185,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8463,6 +9318,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8475,12 +9335,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8598,6 +9468,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8610,12 +9485,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8733,6 +9618,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8745,12 +9635,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
